--- a/ONCHO/Impact Assessments/Nigeria/2025/river statesoem/sites.xlsx
+++ b/ONCHO/Impact Assessments/Nigeria/2025/river statesoem/sites.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\yumbad\Repositories\dsa-forms\ONCHO\Impact Assessments\Nigeria\2025\river statesoem\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B20F9B16-0E88-45D9-9C19-CE762D8555ED}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A0FF77D6-7A6E-4EC2-88A5-D54DCF5EA115}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-28920" yWindow="-120" windowWidth="29040" windowHeight="15840" tabRatio="599" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-28920" yWindow="60" windowWidth="28800" windowHeight="15435" tabRatio="599" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="impact Assessment" sheetId="1" r:id="rId1"/>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="225" uniqueCount="127">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="329" uniqueCount="116">
   <si>
     <t>S/N</t>
   </si>
@@ -128,36 +128,6 @@
     <t>RIV_GOK_M_080</t>
   </si>
   <si>
-    <t>RIV_KHA_M_081</t>
-  </si>
-  <si>
-    <t>ILOLO</t>
-  </si>
-  <si>
-    <t>RIV_KHA_M_082</t>
-  </si>
-  <si>
-    <t>NUMAA-KAA</t>
-  </si>
-  <si>
-    <t>RIV_KHA_M_083</t>
-  </si>
-  <si>
-    <t>KONO/KWAWA</t>
-  </si>
-  <si>
-    <t>RIV_KHA_M_084</t>
-  </si>
-  <si>
-    <t>LUUBAARA</t>
-  </si>
-  <si>
-    <t>RIV_KHA_M_085</t>
-  </si>
-  <si>
-    <t>EEKEN</t>
-  </si>
-  <si>
     <t>RIV_OBA_M_086</t>
   </si>
   <si>
@@ -246,9 +216,6 @@
   </si>
   <si>
     <t>GOKANA</t>
-  </si>
-  <si>
-    <t>KHANA</t>
   </si>
   <si>
     <t>OBIO/AKPOR</t>
@@ -764,13 +731,17 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:XEM56"/>
+  <dimension ref="A1:XEM51"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="2" max="2" width="6.42578125" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="20" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="7.140625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="21.85546875" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="16" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="20.140625" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="7.140625" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="21.85546875" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="21.85546875" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="20.140625" bestFit="1" customWidth="1"/>
     <col min="16368" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
@@ -792,11 +763,19 @@
       </c>
       <c r="F1" s="4"/>
       <c r="G1" s="4"/>
-      <c r="H1" s="4"/>
-      <c r="I1" s="4"/>
+      <c r="H1" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="I1" s="3" t="s">
+        <v>2</v>
+      </c>
       <c r="J1" s="4"/>
-      <c r="K1" s="4"/>
-      <c r="L1" s="4"/>
+      <c r="K1" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="L1" s="3" t="s">
+        <v>3</v>
+      </c>
       <c r="M1" s="4"/>
       <c r="N1" s="4"/>
       <c r="O1" s="4"/>
@@ -17161,13 +17140,25 @@
         <v>4</v>
       </c>
       <c r="C2" s="2" t="s">
-        <v>66</v>
+        <v>56</v>
       </c>
       <c r="D2" t="s">
         <v>6</v>
       </c>
       <c r="E2" s="2" t="s">
-        <v>77</v>
+        <v>66</v>
+      </c>
+      <c r="H2" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="I2" s="2" t="s">
+        <v>56</v>
+      </c>
+      <c r="K2" s="2" t="s">
+        <v>56</v>
+      </c>
+      <c r="L2" s="2" t="s">
+        <v>67</v>
       </c>
     </row>
     <row r="3" spans="1:16367" x14ac:dyDescent="0.25">
@@ -17178,13 +17169,25 @@
         <v>4</v>
       </c>
       <c r="C3" s="2" t="s">
-        <v>66</v>
+        <v>56</v>
       </c>
       <c r="D3" t="s">
         <v>7</v>
       </c>
       <c r="E3" s="2" t="s">
-        <v>78</v>
+        <v>67</v>
+      </c>
+      <c r="H3" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="I3" s="2" t="s">
+        <v>57</v>
+      </c>
+      <c r="K3" s="2" t="s">
+        <v>56</v>
+      </c>
+      <c r="L3" s="2" t="s">
+        <v>66</v>
       </c>
     </row>
     <row r="4" spans="1:16367" x14ac:dyDescent="0.25">
@@ -17195,13 +17198,25 @@
         <v>4</v>
       </c>
       <c r="C4" s="2" t="s">
-        <v>66</v>
+        <v>56</v>
       </c>
       <c r="D4" t="s">
         <v>8</v>
       </c>
       <c r="E4" s="2" t="s">
-        <v>79</v>
+        <v>68</v>
+      </c>
+      <c r="H4" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="I4" s="2" t="s">
+        <v>58</v>
+      </c>
+      <c r="K4" s="2" t="s">
+        <v>56</v>
+      </c>
+      <c r="L4" s="2" t="s">
+        <v>70</v>
       </c>
     </row>
     <row r="5" spans="1:16367" x14ac:dyDescent="0.25">
@@ -17212,13 +17227,25 @@
         <v>4</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>66</v>
+        <v>56</v>
       </c>
       <c r="D5" t="s">
         <v>9</v>
       </c>
       <c r="E5" s="2" t="s">
-        <v>80</v>
+        <v>69</v>
+      </c>
+      <c r="H5" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="I5" s="2" t="s">
+        <v>59</v>
+      </c>
+      <c r="K5" s="2" t="s">
+        <v>56</v>
+      </c>
+      <c r="L5" s="2" t="s">
+        <v>68</v>
       </c>
     </row>
     <row r="6" spans="1:16367" x14ac:dyDescent="0.25">
@@ -17229,13 +17256,25 @@
         <v>4</v>
       </c>
       <c r="C6" s="2" t="s">
-        <v>66</v>
+        <v>56</v>
       </c>
       <c r="D6" t="s">
         <v>10</v>
       </c>
       <c r="E6" s="2" t="s">
-        <v>81</v>
+        <v>70</v>
+      </c>
+      <c r="H6" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="I6" s="2" t="s">
+        <v>60</v>
+      </c>
+      <c r="K6" s="2" t="s">
+        <v>56</v>
+      </c>
+      <c r="L6" s="2" t="s">
+        <v>69</v>
       </c>
     </row>
     <row r="7" spans="1:16367" x14ac:dyDescent="0.25">
@@ -17246,13 +17285,25 @@
         <v>4</v>
       </c>
       <c r="C7" s="2" t="s">
-        <v>67</v>
+        <v>57</v>
       </c>
       <c r="D7" t="s">
         <v>11</v>
       </c>
       <c r="E7" s="2" t="s">
-        <v>82</v>
+        <v>71</v>
+      </c>
+      <c r="H7" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="I7" s="2" t="s">
+        <v>61</v>
+      </c>
+      <c r="K7" s="2" t="s">
+        <v>57</v>
+      </c>
+      <c r="L7" s="2" t="s">
+        <v>73</v>
       </c>
     </row>
     <row r="8" spans="1:16367" x14ac:dyDescent="0.25">
@@ -17263,13 +17314,25 @@
         <v>4</v>
       </c>
       <c r="C8" s="2" t="s">
-        <v>67</v>
+        <v>57</v>
       </c>
       <c r="D8" t="s">
         <v>12</v>
       </c>
       <c r="E8" s="2" t="s">
-        <v>83</v>
+        <v>72</v>
+      </c>
+      <c r="H8" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="I8" s="2" t="s">
+        <v>62</v>
+      </c>
+      <c r="K8" s="2" t="s">
+        <v>57</v>
+      </c>
+      <c r="L8" s="2" t="s">
+        <v>74</v>
       </c>
     </row>
     <row r="9" spans="1:16367" x14ac:dyDescent="0.25">
@@ -17280,13 +17343,25 @@
         <v>4</v>
       </c>
       <c r="C9" s="2" t="s">
-        <v>67</v>
+        <v>57</v>
       </c>
       <c r="D9" t="s">
         <v>13</v>
       </c>
       <c r="E9" s="2" t="s">
-        <v>84</v>
+        <v>73</v>
+      </c>
+      <c r="H9" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="I9" s="2" t="s">
+        <v>63</v>
+      </c>
+      <c r="K9" s="2" t="s">
+        <v>57</v>
+      </c>
+      <c r="L9" s="2" t="s">
+        <v>71</v>
       </c>
     </row>
     <row r="10" spans="1:16367" x14ac:dyDescent="0.25">
@@ -17297,13 +17372,25 @@
         <v>4</v>
       </c>
       <c r="C10" s="2" t="s">
-        <v>67</v>
+        <v>57</v>
       </c>
       <c r="D10" t="s">
         <v>14</v>
       </c>
       <c r="E10" s="2" t="s">
-        <v>85</v>
+        <v>74</v>
+      </c>
+      <c r="H10" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="I10" s="2" t="s">
+        <v>64</v>
+      </c>
+      <c r="K10" s="2" t="s">
+        <v>57</v>
+      </c>
+      <c r="L10" s="2" t="s">
+        <v>72</v>
       </c>
     </row>
     <row r="11" spans="1:16367" x14ac:dyDescent="0.25">
@@ -17314,13 +17401,25 @@
         <v>4</v>
       </c>
       <c r="C11" s="2" t="s">
-        <v>67</v>
+        <v>57</v>
       </c>
       <c r="D11" t="s">
         <v>15</v>
       </c>
       <c r="E11" s="2" t="s">
-        <v>86</v>
+        <v>75</v>
+      </c>
+      <c r="H11" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="I11" s="2" t="s">
+        <v>65</v>
+      </c>
+      <c r="K11" s="2" t="s">
+        <v>57</v>
+      </c>
+      <c r="L11" s="2" t="s">
+        <v>75</v>
       </c>
     </row>
     <row r="12" spans="1:16367" x14ac:dyDescent="0.25">
@@ -17331,13 +17430,19 @@
         <v>4</v>
       </c>
       <c r="C12" s="2" t="s">
-        <v>68</v>
+        <v>58</v>
       </c>
       <c r="D12" t="s">
         <v>16</v>
       </c>
       <c r="E12" s="2" t="s">
-        <v>87</v>
+        <v>76</v>
+      </c>
+      <c r="K12" s="2" t="s">
+        <v>58</v>
+      </c>
+      <c r="L12" s="2" t="s">
+        <v>77</v>
       </c>
     </row>
     <row r="13" spans="1:16367" x14ac:dyDescent="0.25">
@@ -17348,13 +17453,19 @@
         <v>4</v>
       </c>
       <c r="C13" s="2" t="s">
-        <v>68</v>
+        <v>58</v>
       </c>
       <c r="D13" t="s">
         <v>17</v>
       </c>
       <c r="E13" s="2" t="s">
-        <v>88</v>
+        <v>77</v>
+      </c>
+      <c r="K13" s="2" t="s">
+        <v>58</v>
+      </c>
+      <c r="L13" s="2" t="s">
+        <v>76</v>
       </c>
     </row>
     <row r="14" spans="1:16367" x14ac:dyDescent="0.25">
@@ -17365,13 +17476,19 @@
         <v>4</v>
       </c>
       <c r="C14" s="2" t="s">
-        <v>68</v>
+        <v>58</v>
       </c>
       <c r="D14" t="s">
         <v>18</v>
       </c>
       <c r="E14" s="2" t="s">
-        <v>89</v>
+        <v>78</v>
+      </c>
+      <c r="K14" s="2" t="s">
+        <v>58</v>
+      </c>
+      <c r="L14" s="2" t="s">
+        <v>79</v>
       </c>
     </row>
     <row r="15" spans="1:16367" x14ac:dyDescent="0.25">
@@ -17382,13 +17499,19 @@
         <v>4</v>
       </c>
       <c r="C15" s="2" t="s">
-        <v>68</v>
+        <v>58</v>
       </c>
       <c r="D15" t="s">
         <v>19</v>
       </c>
       <c r="E15" s="2" t="s">
-        <v>90</v>
+        <v>79</v>
+      </c>
+      <c r="K15" s="2" t="s">
+        <v>58</v>
+      </c>
+      <c r="L15" s="2" t="s">
+        <v>78</v>
       </c>
     </row>
     <row r="16" spans="1:16367" x14ac:dyDescent="0.25">
@@ -17399,16 +17522,22 @@
         <v>4</v>
       </c>
       <c r="C16" s="2" t="s">
-        <v>68</v>
+        <v>58</v>
       </c>
       <c r="D16" t="s">
         <v>20</v>
       </c>
       <c r="E16" s="2" t="s">
-        <v>91</v>
+        <v>80</v>
+      </c>
+      <c r="K16" s="2" t="s">
+        <v>58</v>
+      </c>
+      <c r="L16" s="2" t="s">
+        <v>80</v>
       </c>
     </row>
-    <row r="17" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A17" s="2">
         <v>16</v>
       </c>
@@ -17416,16 +17545,22 @@
         <v>4</v>
       </c>
       <c r="C17" s="2" t="s">
-        <v>69</v>
+        <v>59</v>
       </c>
       <c r="D17" t="s">
         <v>21</v>
       </c>
       <c r="E17" s="2" t="s">
-        <v>92</v>
+        <v>81</v>
+      </c>
+      <c r="K17" s="2" t="s">
+        <v>59</v>
+      </c>
+      <c r="L17" s="2" t="s">
+        <v>84</v>
       </c>
     </row>
-    <row r="18" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A18" s="2">
         <v>17</v>
       </c>
@@ -17433,16 +17568,22 @@
         <v>4</v>
       </c>
       <c r="C18" s="2" t="s">
-        <v>69</v>
+        <v>59</v>
       </c>
       <c r="D18" t="s">
         <v>22</v>
       </c>
       <c r="E18" s="2" t="s">
-        <v>93</v>
+        <v>82</v>
+      </c>
+      <c r="K18" s="2" t="s">
+        <v>59</v>
+      </c>
+      <c r="L18" s="2" t="s">
+        <v>82</v>
       </c>
     </row>
-    <row r="19" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A19" s="2">
         <v>18</v>
       </c>
@@ -17450,16 +17591,22 @@
         <v>4</v>
       </c>
       <c r="C19" s="2" t="s">
-        <v>69</v>
+        <v>59</v>
       </c>
       <c r="D19" t="s">
         <v>23</v>
       </c>
       <c r="E19" s="2" t="s">
-        <v>94</v>
+        <v>83</v>
+      </c>
+      <c r="K19" s="2" t="s">
+        <v>59</v>
+      </c>
+      <c r="L19" s="2" t="s">
+        <v>85</v>
       </c>
     </row>
-    <row r="20" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A20" s="2">
         <v>19</v>
       </c>
@@ -17467,16 +17614,22 @@
         <v>4</v>
       </c>
       <c r="C20" s="2" t="s">
-        <v>69</v>
+        <v>59</v>
       </c>
       <c r="D20" t="s">
         <v>24</v>
       </c>
       <c r="E20" s="2" t="s">
-        <v>95</v>
+        <v>84</v>
+      </c>
+      <c r="K20" s="2" t="s">
+        <v>59</v>
+      </c>
+      <c r="L20" s="2" t="s">
+        <v>81</v>
       </c>
     </row>
-    <row r="21" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A21" s="2">
         <v>20</v>
       </c>
@@ -17484,16 +17637,22 @@
         <v>4</v>
       </c>
       <c r="C21" s="2" t="s">
-        <v>69</v>
+        <v>59</v>
       </c>
       <c r="D21" t="s">
         <v>25</v>
       </c>
       <c r="E21" s="2" t="s">
-        <v>96</v>
+        <v>85</v>
+      </c>
+      <c r="K21" s="2" t="s">
+        <v>59</v>
+      </c>
+      <c r="L21" s="2" t="s">
+        <v>83</v>
       </c>
     </row>
-    <row r="22" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A22" s="2">
         <v>21</v>
       </c>
@@ -17501,16 +17660,22 @@
         <v>4</v>
       </c>
       <c r="C22" s="2" t="s">
-        <v>70</v>
+        <v>60</v>
       </c>
       <c r="D22" t="s">
         <v>26</v>
       </c>
       <c r="E22" s="2" t="s">
-        <v>97</v>
+        <v>86</v>
+      </c>
+      <c r="K22" s="2" t="s">
+        <v>60</v>
+      </c>
+      <c r="L22" s="2" t="s">
+        <v>86</v>
       </c>
     </row>
-    <row r="23" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A23" s="2">
         <v>22</v>
       </c>
@@ -17518,16 +17683,22 @@
         <v>4</v>
       </c>
       <c r="C23" s="2" t="s">
-        <v>70</v>
+        <v>60</v>
       </c>
       <c r="D23" t="s">
         <v>27</v>
       </c>
       <c r="E23" s="2" t="s">
-        <v>98</v>
+        <v>87</v>
+      </c>
+      <c r="K23" s="2" t="s">
+        <v>60</v>
+      </c>
+      <c r="L23" s="2" t="s">
+        <v>87</v>
       </c>
     </row>
-    <row r="24" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A24" s="2">
         <v>23</v>
       </c>
@@ -17535,16 +17706,22 @@
         <v>4</v>
       </c>
       <c r="C24" s="2" t="s">
-        <v>70</v>
+        <v>60</v>
       </c>
       <c r="D24" t="s">
         <v>28</v>
       </c>
       <c r="E24" s="2" t="s">
-        <v>99</v>
+        <v>88</v>
+      </c>
+      <c r="K24" s="2" t="s">
+        <v>60</v>
+      </c>
+      <c r="L24" s="2" t="s">
+        <v>88</v>
       </c>
     </row>
-    <row r="25" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A25" s="2">
         <v>24</v>
       </c>
@@ -17552,16 +17729,22 @@
         <v>4</v>
       </c>
       <c r="C25" s="2" t="s">
-        <v>70</v>
+        <v>60</v>
       </c>
       <c r="D25" t="s">
         <v>29</v>
       </c>
       <c r="E25" s="2" t="s">
-        <v>100</v>
+        <v>89</v>
+      </c>
+      <c r="K25" s="2" t="s">
+        <v>60</v>
+      </c>
+      <c r="L25" s="2" t="s">
+        <v>90</v>
       </c>
     </row>
-    <row r="26" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A26" s="2">
         <v>25</v>
       </c>
@@ -17569,16 +17752,22 @@
         <v>4</v>
       </c>
       <c r="C26" s="2" t="s">
-        <v>70</v>
+        <v>60</v>
       </c>
       <c r="D26" t="s">
         <v>30</v>
       </c>
       <c r="E26" s="2" t="s">
-        <v>101</v>
+        <v>90</v>
+      </c>
+      <c r="K26" s="2" t="s">
+        <v>60</v>
+      </c>
+      <c r="L26" s="2" t="s">
+        <v>89</v>
       </c>
     </row>
-    <row r="27" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A27" s="2">
         <v>26</v>
       </c>
@@ -17586,16 +17775,22 @@
         <v>4</v>
       </c>
       <c r="C27" s="2" t="s">
-        <v>71</v>
+        <v>61</v>
       </c>
       <c r="D27" t="s">
         <v>31</v>
       </c>
       <c r="E27" s="2" t="s">
-        <v>32</v>
+        <v>91</v>
+      </c>
+      <c r="K27" s="2" t="s">
+        <v>61</v>
+      </c>
+      <c r="L27" s="2" t="s">
+        <v>94</v>
       </c>
     </row>
-    <row r="28" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A28" s="2">
         <v>27</v>
       </c>
@@ -17603,16 +17798,22 @@
         <v>4</v>
       </c>
       <c r="C28" s="2" t="s">
-        <v>71</v>
+        <v>61</v>
       </c>
       <c r="D28" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="E28" s="2" t="s">
-        <v>34</v>
+        <v>92</v>
+      </c>
+      <c r="K28" s="2" t="s">
+        <v>61</v>
+      </c>
+      <c r="L28" s="2" t="s">
+        <v>95</v>
       </c>
     </row>
-    <row r="29" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A29" s="2">
         <v>28</v>
       </c>
@@ -17620,16 +17821,22 @@
         <v>4</v>
       </c>
       <c r="C29" s="2" t="s">
-        <v>71</v>
+        <v>61</v>
       </c>
       <c r="D29" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="E29" s="2" t="s">
-        <v>36</v>
+        <v>93</v>
+      </c>
+      <c r="K29" s="2" t="s">
+        <v>61</v>
+      </c>
+      <c r="L29" s="2" t="s">
+        <v>91</v>
       </c>
     </row>
-    <row r="30" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A30" s="2">
         <v>29</v>
       </c>
@@ -17637,16 +17844,22 @@
         <v>4</v>
       </c>
       <c r="C30" s="2" t="s">
-        <v>71</v>
+        <v>61</v>
       </c>
       <c r="D30" t="s">
-        <v>37</v>
+        <v>34</v>
       </c>
       <c r="E30" s="2" t="s">
-        <v>38</v>
+        <v>94</v>
+      </c>
+      <c r="K30" s="2" t="s">
+        <v>61</v>
+      </c>
+      <c r="L30" s="2" t="s">
+        <v>92</v>
       </c>
     </row>
-    <row r="31" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A31" s="2">
         <v>30</v>
       </c>
@@ -17654,16 +17867,22 @@
         <v>4</v>
       </c>
       <c r="C31" s="2" t="s">
-        <v>71</v>
+        <v>61</v>
       </c>
       <c r="D31" t="s">
-        <v>39</v>
+        <v>35</v>
       </c>
       <c r="E31" s="2" t="s">
-        <v>40</v>
+        <v>95</v>
+      </c>
+      <c r="K31" s="2" t="s">
+        <v>61</v>
+      </c>
+      <c r="L31" s="2" t="s">
+        <v>93</v>
       </c>
     </row>
-    <row r="32" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A32" s="2">
         <v>31</v>
       </c>
@@ -17671,16 +17890,22 @@
         <v>4</v>
       </c>
       <c r="C32" s="2" t="s">
-        <v>72</v>
+        <v>62</v>
       </c>
       <c r="D32" t="s">
-        <v>41</v>
+        <v>36</v>
       </c>
       <c r="E32" s="2" t="s">
-        <v>102</v>
+        <v>96</v>
+      </c>
+      <c r="K32" s="2" t="s">
+        <v>62</v>
+      </c>
+      <c r="L32" s="2" t="s">
+        <v>97</v>
       </c>
     </row>
-    <row r="33" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A33" s="2">
         <v>32</v>
       </c>
@@ -17688,16 +17913,22 @@
         <v>4</v>
       </c>
       <c r="C33" s="2" t="s">
-        <v>72</v>
+        <v>62</v>
       </c>
       <c r="D33" t="s">
-        <v>42</v>
+        <v>37</v>
       </c>
       <c r="E33" s="2" t="s">
-        <v>103</v>
+        <v>97</v>
+      </c>
+      <c r="K33" s="2" t="s">
+        <v>62</v>
+      </c>
+      <c r="L33" s="2" t="s">
+        <v>99</v>
       </c>
     </row>
-    <row r="34" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A34" s="2">
         <v>33</v>
       </c>
@@ -17705,16 +17936,22 @@
         <v>4</v>
       </c>
       <c r="C34" s="2" t="s">
-        <v>72</v>
+        <v>62</v>
       </c>
       <c r="D34" t="s">
-        <v>43</v>
+        <v>38</v>
       </c>
       <c r="E34" s="2" t="s">
-        <v>104</v>
+        <v>98</v>
+      </c>
+      <c r="K34" s="2" t="s">
+        <v>62</v>
+      </c>
+      <c r="L34" s="2" t="s">
+        <v>98</v>
       </c>
     </row>
-    <row r="35" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A35" s="2">
         <v>34</v>
       </c>
@@ -17722,16 +17959,22 @@
         <v>4</v>
       </c>
       <c r="C35" s="2" t="s">
-        <v>72</v>
+        <v>62</v>
       </c>
       <c r="D35" t="s">
-        <v>44</v>
+        <v>39</v>
       </c>
       <c r="E35" s="2" t="s">
-        <v>105</v>
+        <v>99</v>
+      </c>
+      <c r="K35" s="2" t="s">
+        <v>62</v>
+      </c>
+      <c r="L35" s="2" t="s">
+        <v>96</v>
       </c>
     </row>
-    <row r="36" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A36" s="2">
         <v>35</v>
       </c>
@@ -17739,16 +17982,22 @@
         <v>4</v>
       </c>
       <c r="C36" s="2" t="s">
-        <v>72</v>
+        <v>62</v>
       </c>
       <c r="D36" t="s">
-        <v>45</v>
+        <v>40</v>
       </c>
       <c r="E36" s="2" t="s">
-        <v>106</v>
+        <v>100</v>
+      </c>
+      <c r="K36" s="2" t="s">
+        <v>62</v>
+      </c>
+      <c r="L36" s="2" t="s">
+        <v>100</v>
       </c>
     </row>
-    <row r="37" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A37" s="2">
         <v>36</v>
       </c>
@@ -17756,16 +18005,22 @@
         <v>4</v>
       </c>
       <c r="C37" s="2" t="s">
-        <v>73</v>
+        <v>63</v>
       </c>
       <c r="D37" t="s">
-        <v>46</v>
+        <v>41</v>
       </c>
       <c r="E37" s="2" t="s">
-        <v>107</v>
+        <v>101</v>
+      </c>
+      <c r="K37" s="2" t="s">
+        <v>63</v>
+      </c>
+      <c r="L37" s="2" t="s">
+        <v>105</v>
       </c>
     </row>
-    <row r="38" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A38" s="2">
         <v>37</v>
       </c>
@@ -17773,16 +18028,22 @@
         <v>4</v>
       </c>
       <c r="C38" s="2" t="s">
-        <v>73</v>
+        <v>63</v>
       </c>
       <c r="D38" t="s">
-        <v>47</v>
+        <v>42</v>
       </c>
       <c r="E38" s="2" t="s">
-        <v>108</v>
+        <v>102</v>
+      </c>
+      <c r="K38" s="2" t="s">
+        <v>63</v>
+      </c>
+      <c r="L38" s="2" t="s">
+        <v>104</v>
       </c>
     </row>
-    <row r="39" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A39" s="2">
         <v>38</v>
       </c>
@@ -17790,16 +18051,22 @@
         <v>4</v>
       </c>
       <c r="C39" s="2" t="s">
-        <v>73</v>
+        <v>63</v>
       </c>
       <c r="D39" t="s">
-        <v>48</v>
+        <v>43</v>
       </c>
       <c r="E39" s="2" t="s">
-        <v>109</v>
+        <v>103</v>
+      </c>
+      <c r="K39" s="2" t="s">
+        <v>63</v>
+      </c>
+      <c r="L39" s="2" t="s">
+        <v>103</v>
       </c>
     </row>
-    <row r="40" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A40" s="2">
         <v>39</v>
       </c>
@@ -17807,16 +18074,22 @@
         <v>4</v>
       </c>
       <c r="C40" s="2" t="s">
-        <v>73</v>
+        <v>63</v>
       </c>
       <c r="D40" t="s">
-        <v>49</v>
+        <v>44</v>
       </c>
       <c r="E40" s="2" t="s">
-        <v>110</v>
+        <v>104</v>
+      </c>
+      <c r="K40" s="2" t="s">
+        <v>63</v>
+      </c>
+      <c r="L40" s="2" t="s">
+        <v>102</v>
       </c>
     </row>
-    <row r="41" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A41" s="2">
         <v>40</v>
       </c>
@@ -17824,16 +18097,22 @@
         <v>4</v>
       </c>
       <c r="C41" s="2" t="s">
-        <v>73</v>
+        <v>63</v>
       </c>
       <c r="D41" t="s">
-        <v>50</v>
+        <v>45</v>
       </c>
       <c r="E41" s="2" t="s">
-        <v>111</v>
+        <v>105</v>
+      </c>
+      <c r="K41" s="2" t="s">
+        <v>63</v>
+      </c>
+      <c r="L41" s="2" t="s">
+        <v>101</v>
       </c>
     </row>
-    <row r="42" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A42" s="2">
         <v>41</v>
       </c>
@@ -17841,16 +18120,22 @@
         <v>4</v>
       </c>
       <c r="C42" s="2" t="s">
-        <v>74</v>
+        <v>64</v>
       </c>
       <c r="D42" t="s">
-        <v>51</v>
+        <v>46</v>
       </c>
       <c r="E42" s="2" t="s">
-        <v>112</v>
+        <v>106</v>
+      </c>
+      <c r="K42" s="2" t="s">
+        <v>64</v>
+      </c>
+      <c r="L42" s="2" t="s">
+        <v>107</v>
       </c>
     </row>
-    <row r="43" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A43" s="2">
         <v>42</v>
       </c>
@@ -17858,16 +18143,22 @@
         <v>4</v>
       </c>
       <c r="C43" s="2" t="s">
-        <v>74</v>
+        <v>64</v>
       </c>
       <c r="D43" t="s">
-        <v>52</v>
+        <v>47</v>
       </c>
       <c r="E43" s="2" t="s">
-        <v>113</v>
+        <v>107</v>
+      </c>
+      <c r="K43" s="2" t="s">
+        <v>64</v>
+      </c>
+      <c r="L43" s="2" t="s">
+        <v>109</v>
       </c>
     </row>
-    <row r="44" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A44" s="2">
         <v>43</v>
       </c>
@@ -17875,16 +18166,22 @@
         <v>4</v>
       </c>
       <c r="C44" s="2" t="s">
-        <v>74</v>
+        <v>64</v>
       </c>
       <c r="D44" t="s">
-        <v>53</v>
+        <v>48</v>
       </c>
       <c r="E44" s="2" t="s">
-        <v>114</v>
+        <v>108</v>
+      </c>
+      <c r="K44" s="2" t="s">
+        <v>64</v>
+      </c>
+      <c r="L44" s="2" t="s">
+        <v>106</v>
       </c>
     </row>
-    <row r="45" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A45" s="2">
         <v>44</v>
       </c>
@@ -17892,16 +18189,22 @@
         <v>4</v>
       </c>
       <c r="C45" s="2" t="s">
-        <v>74</v>
+        <v>64</v>
       </c>
       <c r="D45" t="s">
-        <v>54</v>
+        <v>49</v>
       </c>
       <c r="E45" s="2" t="s">
-        <v>115</v>
+        <v>109</v>
+      </c>
+      <c r="K45" s="2" t="s">
+        <v>64</v>
+      </c>
+      <c r="L45" s="2" t="s">
+        <v>108</v>
       </c>
     </row>
-    <row r="46" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="46" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A46" s="2">
         <v>45</v>
       </c>
@@ -17909,16 +18212,22 @@
         <v>4</v>
       </c>
       <c r="C46" s="2" t="s">
-        <v>74</v>
+        <v>64</v>
       </c>
       <c r="D46" t="s">
-        <v>55</v>
+        <v>50</v>
       </c>
       <c r="E46" s="2" t="s">
-        <v>116</v>
+        <v>110</v>
+      </c>
+      <c r="K46" s="2" t="s">
+        <v>64</v>
+      </c>
+      <c r="L46" s="2" t="s">
+        <v>110</v>
       </c>
     </row>
-    <row r="47" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="47" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A47" s="2">
         <v>46</v>
       </c>
@@ -17926,16 +18235,22 @@
         <v>4</v>
       </c>
       <c r="C47" s="2" t="s">
-        <v>75</v>
+        <v>65</v>
       </c>
       <c r="D47" t="s">
-        <v>56</v>
+        <v>51</v>
       </c>
       <c r="E47" s="2" t="s">
-        <v>117</v>
+        <v>111</v>
+      </c>
+      <c r="K47" s="2" t="s">
+        <v>65</v>
+      </c>
+      <c r="L47" s="2" t="s">
+        <v>112</v>
       </c>
     </row>
-    <row r="48" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="48" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A48" s="2">
         <v>47</v>
       </c>
@@ -17943,16 +18258,22 @@
         <v>4</v>
       </c>
       <c r="C48" s="2" t="s">
-        <v>75</v>
+        <v>65</v>
       </c>
       <c r="D48" t="s">
-        <v>57</v>
+        <v>52</v>
       </c>
       <c r="E48" s="2" t="s">
-        <v>118</v>
+        <v>112</v>
+      </c>
+      <c r="K48" s="2" t="s">
+        <v>65</v>
+      </c>
+      <c r="L48" s="2" t="s">
+        <v>114</v>
       </c>
     </row>
-    <row r="49" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="49" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A49" s="2">
         <v>48</v>
       </c>
@@ -17960,16 +18281,22 @@
         <v>4</v>
       </c>
       <c r="C49" s="2" t="s">
-        <v>75</v>
+        <v>65</v>
       </c>
       <c r="D49" t="s">
-        <v>58</v>
+        <v>53</v>
       </c>
       <c r="E49" s="2" t="s">
-        <v>119</v>
+        <v>113</v>
+      </c>
+      <c r="K49" s="2" t="s">
+        <v>65</v>
+      </c>
+      <c r="L49" s="2" t="s">
+        <v>113</v>
       </c>
     </row>
-    <row r="50" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="50" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A50" s="2">
         <v>49</v>
       </c>
@@ -17977,16 +18304,22 @@
         <v>4</v>
       </c>
       <c r="C50" s="2" t="s">
-        <v>75</v>
+        <v>65</v>
       </c>
       <c r="D50" t="s">
-        <v>59</v>
+        <v>54</v>
       </c>
       <c r="E50" s="2" t="s">
-        <v>120</v>
+        <v>114</v>
+      </c>
+      <c r="K50" s="2" t="s">
+        <v>65</v>
+      </c>
+      <c r="L50" s="2" t="s">
+        <v>111</v>
       </c>
     </row>
-    <row r="51" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="51" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A51" s="2">
         <v>50</v>
       </c>
@@ -17994,101 +18327,26 @@
         <v>4</v>
       </c>
       <c r="C51" s="2" t="s">
-        <v>75</v>
+        <v>65</v>
       </c>
       <c r="D51" t="s">
-        <v>60</v>
+        <v>55</v>
       </c>
       <c r="E51" s="2" t="s">
-        <v>121</v>
-      </c>
-    </row>
-    <row r="52" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A52" s="2">
-        <v>51</v>
-      </c>
-      <c r="B52" s="2" t="s">
-        <v>4</v>
-      </c>
-      <c r="C52" s="2" t="s">
-        <v>76</v>
-      </c>
-      <c r="D52" t="s">
-        <v>61</v>
-      </c>
-      <c r="E52" s="2" t="s">
-        <v>122</v>
-      </c>
-    </row>
-    <row r="53" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A53" s="2">
-        <v>52</v>
-      </c>
-      <c r="B53" s="2" t="s">
-        <v>4</v>
-      </c>
-      <c r="C53" s="2" t="s">
-        <v>76</v>
-      </c>
-      <c r="D53" t="s">
-        <v>62</v>
-      </c>
-      <c r="E53" s="2" t="s">
-        <v>123</v>
-      </c>
-    </row>
-    <row r="54" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A54" s="2">
-        <v>53</v>
-      </c>
-      <c r="B54" s="2" t="s">
-        <v>4</v>
-      </c>
-      <c r="C54" s="2" t="s">
-        <v>76</v>
-      </c>
-      <c r="D54" t="s">
-        <v>63</v>
-      </c>
-      <c r="E54" s="2" t="s">
-        <v>124</v>
-      </c>
-    </row>
-    <row r="55" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A55" s="2">
-        <v>54</v>
-      </c>
-      <c r="B55" s="2" t="s">
-        <v>4</v>
-      </c>
-      <c r="C55" s="2" t="s">
-        <v>76</v>
-      </c>
-      <c r="D55" t="s">
-        <v>64</v>
-      </c>
-      <c r="E55" s="2" t="s">
-        <v>125</v>
-      </c>
-    </row>
-    <row r="56" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A56" s="2">
-        <v>55</v>
-      </c>
-      <c r="B56" s="2" t="s">
-        <v>4</v>
-      </c>
-      <c r="C56" s="2" t="s">
-        <v>76</v>
-      </c>
-      <c r="D56" t="s">
+        <v>115</v>
+      </c>
+      <c r="K51" s="2" t="s">
         <v>65</v>
       </c>
-      <c r="E56" s="2" t="s">
-        <v>126</v>
+      <c r="L51" s="2" t="s">
+        <v>115</v>
       </c>
     </row>
   </sheetData>
+  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="K2:L51">
+    <sortCondition ref="K2:K51"/>
+    <sortCondition ref="L2:L51"/>
+  </sortState>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait"/>
